--- a/results/log_pv_cap_fit/log_pv_cap_fit_densities_fdensity_estimates.xlsx
+++ b/results/log_pv_cap_fit/log_pv_cap_fit_densities_fdensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_cap_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_cap_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_cap_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_cap_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_cap_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_cap_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fdensity</t>
+          <t>D(Firms)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.010***</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.061***</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.061***</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.061***</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.004</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.004</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.004</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.319***</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-0.732***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-0.732***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-0.732***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2.128***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2.128***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.128***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,43 +616,13 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>0.003*</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.013</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.013</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.013</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,126 +668,96 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>0.158***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.241</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.241</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.241</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.234***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.234***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.234***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_fdensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>0.900***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.010*</t>
+          <t>0.748***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.015***</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.626***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.958***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.810***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.707***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.401*</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.589***</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.839***</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.977***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.908***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.852***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Firms))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.059***</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.008*</t>
+          <t>-0.010*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.008***</t>
+          <t>-0.015***</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.230***</t>
+          <t>0.401*</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.287***</t>
+          <t>0.589***</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.314***</t>
+          <t>0.839***</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_cap_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.900***</t>
+          <t>-0.059***</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.748***</t>
+          <t>-0.008*</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.626***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.958***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.810***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.707***</t>
-        </is>
-      </c>
+          <t>-0.008***</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>-0.230***</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>-0.287***</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.846</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.881</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.862</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.840</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.228</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.422</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.478</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.154</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.154</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.154</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.101</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.101</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.101</t>
-        </is>
-      </c>
+          <t>-0.314***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-10022.667</t>
+          <t>0.882</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9570.163</t>
+          <t>0.864</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-9299.041</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-10001.786</t>
+          <t>0.881</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9495.820</t>
+          <t>0.862</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9148.417</t>
+          <t>0.840</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10006.541</t>
+          <t>0.228</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-9395.264</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8948.661</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1403.600</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1403.600</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1403.600</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2879.849</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2879.849</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2879.849</t>
+          <t>0.478</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-9971.923</t>
+          <t>-10022.667</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-9519.419</t>
+          <t>-9570.163</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-9248.298</t>
+          <t>-9299.041</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-9973.595</t>
+          <t>-10001.786</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9467.629</t>
+          <t>-9495.820</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9120.226</t>
+          <t>-9148.417</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-9983.988</t>
+          <t>-10006.541</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-9372.711</t>
+          <t>-9395.264</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8926.109</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1431.791</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1431.791</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1431.791</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2908.040</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2908.040</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2908.040</t>
+          <t>-8948.661</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5020.333</t>
+          <t>-9971.923</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4794.081</t>
+          <t>-9519.419</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4658.521</t>
+          <t>-9248.298</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5005.893</t>
+          <t>-9973.595</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4752.910</t>
+          <t>-9467.629</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4579.209</t>
+          <t>-9120.226</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5007.271</t>
+          <t>-9983.988</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4701.632</t>
+          <t>-9372.711</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4478.331</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-696.800</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-696.800</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>-696.800</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-1434.925</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1434.925</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-1434.925</t>
+          <t>-8926.109</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>5020.333</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4794.081</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4658.521</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>5005.893</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4752.910</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4579.209</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>5007.271</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4701.632</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>4478.331</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    66.689581   1      0.0
-1  LM Marginal Spatial (LM2)    19.038856   1      0.0
-2             LM Joint (LMJ)  4809.978204   2      0.0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    66.689581   1      0.0
-1  LM Marginal Spatial (LM2)     8.998724   1      0.0
-2             LM Joint (LMJ)  4528.477206   2      0.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    66.689581   1      0.0
-1  LM Marginal Spatial (LM2)     8.609186   1      0.0
-2             LM Joint (LMJ)  4521.618256   2      0.0</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial  172.284513  1     0.0
-1  Hausman Specification Test -158.267894  4     1.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   42.572582  1     0.0
-1  Hausman Specification Test -158.267894  4     1.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   28.940599  1     0.0
-1  Hausman Specification Test -158.267894  4     1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           fdensity     0.008634  0.001344    6.42336       0.0
-1         log_income     0.050659  0.069703   0.726786  0.467357
-2         log_hholds      0.00077  0.001134   0.679606  0.496754
-3    log_sunny_hours     0.114537  0.032682   3.504559  0.000457
-4         W_fdensity    -0.009931  0.025883    -0.3837  0.701201
-5       W_log_income     0.400844  0.161903   2.475829  0.013293
-6       W_log_hholds    -0.059138  0.017562  -3.367461  0.000759
-7  W_log_sunny_hours    -0.230007  0.051982  -4.424739   0.00001
-8   W_log_pv_cap_fit     0.899751  0.024309  37.012344       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           fdensity     0.008011  0.001458   5.494515       0.0
-1         log_income     0.104472  0.071335   1.464512  0.143054
-2         log_hholds     0.001282  0.001224   1.047729  0.294763
-3    log_sunny_hours     0.107042  0.033287   3.215682  0.001301
-4         W_fdensity     -0.01006  0.004034  -2.493734  0.012641
-5       W_log_income     0.588765  0.090132   6.532236       0.0
-6       W_log_hholds     -0.00818  0.003632  -2.252115  0.024315
-7  W_log_sunny_hours     -0.28743  0.044034  -6.527403       0.0
-8   W_log_pv_cap_fit     0.747918  0.018698  39.999863       0.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           fdensity     0.007741  0.001546   5.008576  0.000001
-1         log_income     0.163748  0.072688   2.252765  0.024274
-2         log_hholds     0.001441  0.001294   1.113499  0.265494
-3    log_sunny_hours     0.086234  0.034559   2.495256  0.012587
-4         W_fdensity    -0.014976  0.003244  -4.617037  0.000004
-5       W_log_income     0.838504  0.085676   9.786878       0.0
-6       W_log_hholds    -0.007851  0.002112  -3.717015  0.000202
-7  W_log_sunny_hours    -0.313777  0.043231  -7.258202       0.0
-8   W_log_pv_cap_fit     0.626143  0.020343  30.778625       0.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          fdensity      0.00819  0.001343   6.097382       0.0
-1        log_income     0.042296  0.030608   1.381869  0.167012
-2        log_hholds     0.000884   0.00113   0.782602  0.433861
-3   log_sunny_hours     0.034456  0.022823   1.509665  0.131129
-4  W_log_pv_cap_fit     0.958145  0.010888  88.003039       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          fdensity     0.007817  0.001452   5.384249       0.0
-1        log_income     0.386407  0.037157  10.399347       0.0
-2        log_hholds     0.001439  0.001221   1.178782  0.238485
-3   log_sunny_hours    -0.007635  0.023885  -0.319674  0.749216
-4  W_log_pv_cap_fit     0.809844  0.014228  56.920209       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          fdensity     0.007761  0.001565   4.960207  0.000001
-1        log_income     0.607232  0.042237  14.376739       0.0
-2        log_hholds     0.001393  0.001314   1.059811   0.28923
-3   log_sunny_hours    -0.028456  0.025701  -1.107219  0.268199
-4  W_log_pv_cap_fit     0.707076  0.016384  43.157367       0.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         fdensity     0.008497  0.001343    6.326326       0.0
-1       log_income     0.066502  0.069404    0.958181  0.337971
-2       log_hholds     0.001146  0.001126    1.018397   0.30849
-3  log_sunny_hours     0.114628  0.032704    3.504949  0.000457
-4           lambda     0.976686  0.006505  150.139204       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         fdensity     0.008775  0.001408    6.233149       0.0
-1       log_income     0.211709   0.06912    3.062938  0.002192
-2       log_hholds      0.00238  0.001157    2.057016  0.039685
-3  log_sunny_hours     0.141992  0.033422    4.248398  0.000022
-4           lambda     0.908312  0.008747  103.844021       0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         fdensity     0.010382  0.001521   6.827955       0.0
-1       log_income     0.318973  0.070074   4.551935  0.000005
-2       log_hholds     0.002865  0.001161   2.467108  0.013621
-3  log_sunny_hours     0.157815   0.03527   4.474442  0.000008
-4           lambda     0.851711  0.011757  72.444747       0.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     6.023135  0.536074   11.23565       0.0
-1         fdensity    -0.060854  0.005226 -11.645285       0.0
-2       log_income     -0.73223  0.085361  -8.578024       0.0
-3       log_hholds     0.012544  0.009034   1.388582  0.165109
-4  log_sunny_hours     0.240613  0.162286   1.482652  0.138319</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     6.023135  0.536074   11.23565       0.0
-1         fdensity    -0.060854  0.005226 -11.645285       0.0
-2       log_income     -0.73223  0.085361  -8.578024       0.0
-3       log_hholds     0.012544  0.009034   1.388582  0.165109
-4  log_sunny_hours     0.240613  0.162286   1.482652  0.138319</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     6.023135  0.536074   11.23565       0.0
-1         fdensity    -0.060854  0.005226 -11.645285       0.0
-2       log_income     -0.73223  0.085361  -8.578024       0.0
-3       log_hholds     0.012544  0.009034   1.388582  0.165109
-4  log_sunny_hours     0.240613  0.162286   1.482652  0.138319</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.691025   0.21584  -21.73381       0.0
-1         fdensity     0.003812  0.002674   1.425818  0.153921
-2       log_income     2.128377  0.045679  46.594161       0.0
-3       log_hholds     0.000019  0.002284   0.008391  0.993305
-4  log_sunny_hours    -0.234135  0.044633  -5.245748       0.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.691025   0.21584  -21.73381       0.0
-1         fdensity     0.003812  0.002674   1.425818  0.153921
-2       log_income     2.128377  0.045679  46.594161       0.0
-3       log_hholds     0.000019  0.002284   0.008391  0.993305
-4  log_sunny_hours    -0.234135  0.044633  -5.245748       0.0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.691025   0.21584  -21.73381       0.0
-1         fdensity     0.003812  0.002674   1.425818  0.153921
-2       log_income     2.128377  0.045679  46.594161       0.0
-3       log_hholds     0.000019  0.002284   0.008391  0.993305
-4  log_sunny_hours    -0.234135  0.044633  -5.245748       0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-fdensity                                    -0.012935   
-log_income                                   4.503821   
-log_hholds                                  -0.582228   
-log_sunny_hours                             -1.151840   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-fdensity                                      0.008634   
-log_income                                    0.050659   
-log_hholds                                    0.000770   
-log_sunny_hours                               0.114537   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-fdensity                                       -0.021570  
-log_income                                      4.453162  
-log_hholds                                     -0.582999  
-log_sunny_hours                                -1.266376  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-fdensity                             -0.008129   
-log_income                            2.750045   
-log_hholds                           -0.027364   
-log_sunny_hours                      -0.715595   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-fdensity                               0.008011   
-log_income                             0.104472   
-log_hholds                             0.001282   
-log_sunny_hours                        0.107042   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-fdensity                                -0.016140  
-log_income                               2.645573  
-log_hholds                              -0.028646  
-log_sunny_hours                         -0.822637  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-fdensity                         -0.019352                    0.007741   
-log_income                        2.680842                    0.163748   
-log_hholds                       -0.017146                    0.001441   
-log_sunny_hours                  -0.608635                    0.086234   
-                 indirect_ML_LagFE(SLX)_queen  
-fdensity                            -0.027093  
-log_income                           2.517093  
-log_hholds                          -0.018586  
-log_sunny_hours                     -0.694869  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-fdensity                                0.195684   
-log_income                              1.010530   
-log_hholds                              0.021126   
-log_sunny_hours                         0.823217   
-                 direct_ML_LagFE_inverse_distance  \
-fdensity                                 0.008190   
-log_income                               0.042296   
-log_hholds                               0.000884   
-log_sunny_hours                          0.034456   
-                 indirect_ML_LagFE_inverse_distance  
-fdensity                                   0.187493  
-log_income                                 0.968234  
-log_hholds                                 0.020242  
-log_sunny_hours                            0.788761  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-fdensity                         0.041111                   0.007817   
-log_income                       2.032052                   0.386407   
-log_hholds                       0.007566                   0.001439   
-log_sunny_hours                 -0.040154                  -0.007635   
-                 indirect_ML_LagFE_k_nearest  
-fdensity                            0.033293  
-log_income                          1.645645  
-log_hholds                          0.006128  
-log_sunny_hours                    -0.032518  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-fdensity                     0.026493               0.007761   
-log_income                   2.073003               0.607232   
-log_hholds                   0.004755               0.001393   
-log_sunny_hours             -0.097146              -0.028456   
-                 indirect_ML_LagFE_queen  
-fdensity                        0.018733  
-log_income                      1.465771  
-log_hholds                      0.003362  
-log_sunny_hours                -0.068689  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.977***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.908***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.852***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>6.023***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>6.023***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>6.023***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-4.691***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-4.691***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-4.691***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
